--- a/Agreement and discrepancy taxonomy/3. comparison_with_vs_without_AI.xlsx
+++ b/Agreement and discrepancy taxonomy/3. comparison_with_vs_without_AI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pp3\SECM-CAT\Agreement and discrepancy taxonomy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1\repositorios\SECM-CAT\Agreement and discrepancy taxonomy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93836B2A-B4C5-4252-AFF6-08019D3C7A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA940D4-FB59-4B5C-8428-2D8EAEE8C4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="66 discrepancies " sheetId="1" r:id="rId1"/>
@@ -36,9 +36,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1561,9 +1558,6 @@
     <t>A scan of the application's web backend is required to rule out vulnerabilities associated with poor randomization and incidents of loss of access to generated tokens in endpoints.</t>
   </si>
   <si>
-    <t>Real-time application execution was required, and it was verified that the application logs out after a period of inactivity to prevent unauthorized access, particularly in high-risk locations or when handling sensitive data.</t>
-  </si>
-  <si>
     <t>You need to log out from the application to verify that the successful logout message is displayed.</t>
   </si>
   <si>
@@ -1712,6 +1706,9 @@
   </si>
   <si>
     <t>You must run the application and navigate through it to determine if it has feedback channels within its views</t>
+  </si>
+  <si>
+    <t>It was necessary to review the source code to verify that, after closing the session, all temporary files are deleted at the end of the session, in order to prevent unauthorized access to confidential data.</t>
   </si>
 </sst>
 </file>
@@ -1902,133 +1899,10 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ComparisonTable" displayName="ComparisonTable" ref="A1:E470">
-  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A1:E470" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="4">
+  <autoFilter ref="A1:E470" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="3">
       <filters>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <x14:filter val="Fue necesaria una inspección de código en la que se detectó que existía una posibilidad de command injection"/>
-            <x14:filter val="Fue necesaria una revisión del código fuente de la aplicación y  the application code reveals no functionality to capture the user's most recent activity date"/>
-            <x14:filter val="fue necesario acceder al código de la aplicación Android para verificar que has been verified that in the AndroidManifest.xml file a BroadcastReceiver has the configuration android:exported=&quot;false&quot;"/>
-            <x14:filter val="Fue necesario acceder al código fuente de la aplicación y verificar que no se ocupen modos deprecados, for instance  MODE_WORLD_READABLE is not implemented, nor was the use of sockets identified, therefore the requirement is met"/>
-            <x14:filter val="Fue necesario buscar en el código fuente de la aplicación para evidenciar que no se implementa llamadas a System.loadLibrary(), DexClassLoader, por lo tanto cumple con seguridad por diseño"/>
-            <x14:filter val="Fue necesario desinstalar la aplicación de manera manual y verificar vía comandos que confidential user data are deleted luego de desinstalar"/>
-            <x14:filter val="Fue necesario ejecutar la aplicación y evaluar si al pasar a segundo plano se limpiaba los datos sensibles, al ejecutar no superó la prueba"/>
-            <x14:filter val="Fue necesario ingresar al backend de la aplicación a través de la versión Web y se verifico que the web application's user and credential management module allows you to configure temporary passwords, which require an immediate change to a permanent password upon first login"/>
-            <x14:filter val="Fue necesario ingresar al Backend de la aplicación y verificar se implementen procedimientos de gestión de contraseñas seguras"/>
-            <x14:filter val="Fue necesario ingresar al código de la aplicación Android y verificar que  BroadcastReceiver with the android:exported=&quot;false&quot; configuration has been detected in the AndroidManifest.xml file"/>
-            <x14:filter val="Fue necesario ingresar al código fuente de la aplicación para verificar que _x0009_No intents, transmissions, or permissions related to SMS/MMS were identified, and there is no evidence of functional flows or SMS-based transmissions that handle confidential data; therefore, the scenario regulated by this requirement is not activated for the mobile application"/>
-            <x14:filter val="Fue necesario ingresar al código fuente de la aplicación y dentro del fichero AndroidManifest.xml se evidenció que no user-defined permissions or new permissions outside of the standard ones are being used"/>
-            <x14:filter val="Fue necesario ingresar al código fuente de la aplicación y en el build.gradle no se detectó llamadas a código nativo. Adicionalmente no se tiene hallazgos de manejo inseguro de memoria"/>
-            <x14:filter val="Fue necesario ingresar al cóigo fuente de la aplicación y erificar que no se encuentra habilitado JS, por lo que cumpliría a través de diseño seguro por defecto"/>
-            <x14:filter val="Fue necesario ingresar y revisar el código fuente para detectar si se implementa factor doble autenticación FMA, o SMS sendig, por lo que al no existir dicha funcionalidad, no existe vector de ataque"/>
-            <x14:filter val="Fue necesario inspeccionar el código fuente para verificar si se encontraba en primera instancia habilitado o no webviews, al no encontrarse implementada esta funcionalidad, se declara cumplimiento puesto que no hay vector de ataque"/>
-            <x14:filter val="Fue necesario realizar un análisis de código dinámico al backend de la aplicación web para verificar que hay missing headers and configurations in the backend to better manage http/https requests"/>
-            <x14:filter val="Fue necesario revisar el código fuente de la aplicación y se encontró que no se tiene habilitado JS ni Webviews, debido a seguridad por diseño no se tienen vectores de ataque sobre carga dinámica de código"/>
-            <x14:filter val="Fue necesario revisar el código fuente minuciosamente para verificar que  the session ID is not being used in the URL in HTTP requests"/>
-            <x14:filter val="Fue necesario revisar la documentación el Backend de la aplicación para evidenciar que eisten controles para consumir las apis expuestas"/>
-            <x14:filter val="Fue necesario revisar la documentación y código fuente y there is no evidence of explicit segregation in storage or configuration/control files in a directory separate from user data"/>
-            <x14:filter val="Fue necesario revisar la funcionalidad de la aplicación web backend y there is a function to match patients by certain criteria, including UUID"/>
-            <x14:filter val="Fue necesario un escaneo del backend de la aplicación para detectar si habría issues sobre manejo inadecuado de memoria como use-after-free errors , no se encontraron issues"/>
-            <x14:filter val="Fue necesario un escaneo del backend de la aplicación para detectar si habría issues sobre manejo inadecuado de memoria, no se encontraron issues"/>
-            <x14:filter val="Fue necesario una inspección del código fuente de la aplicación para detectar que la característica de no toucheable no se encontraba implementada, por lo que no prevendría prevent tapjacking attacks"/>
-            <x14:filter val="Fue necesario una instalación de teclados de terceras personas y verificar que la aplicación no permita el ingreso de datos desde el mismo"/>
-            <x14:filter val="Fue necesario verificar que la aplicación emplee mecanismos adicionales para asegurar las solicitudes de red basadas en protocolo http"/>
-            <x14:filter val="Fue necesario verificar que la aplicación en tiempo de ejecución emplee credenciales únicas para autenticación, en este caso se usa usuario y password"/>
-            <x14:filter val="Fuen necesario correr la aplicación para verificar que running the app, we observed that the clipboard allows users to copy and paste the username and password for login"/>
-            <x14:filter val="No se encontraron vulnerabilidades asociadas a desbordamiento de buffer al realizar un escaneo del backend de la aplicación, así mismo no se encontró la vulnerabilidad en el código fuente de la apk"/>
-            <x14:filter val="requería acceder al código fuente, buscar la implementación de SSLSocketFactory  y verificar que se cumpla con la medida de seguridad checkServerTrusted"/>
-            <x14:filter val="Requería ingresar a la aplicación y verificar que durante la frase de autenticación no se muestren mensajes de ayuda ni feedbak"/>
-            <x14:filter val="requirió a validation of the code signature via comandos para confirmar el cumplimiento"/>
-            <x14:filter val="requirió navegar en el código fuente de la aplicación para verificar si key credentials are loaded securely using environment variables"/>
-            <x14:filter val="Requirió revisar el código de la aplicación y no mechanisms have been found to restrict connection times to high-risk EHRi services to improve security and minimize the risk of unauthorized access"/>
-            <x14:filter val="Requirió una revisión manual code, and it is verified that WebViews functionality is not implemented, therefore, control is considered to be fulfilled by design"/>
-            <x14:filter val="Requirió una revisión y análisis de la funcionalidad, consecuentemente no se encontraron mecanismos para restrict connection times to high-risk EHRi services to enhance security and minimize the risk of unauthorized access"/>
-            <x14:filter val="Se accedió al backend de la aplicación para gestión de usuarios y se pudo comprobar que se permite configure temporary passwords, which require an immediate change to a permanent password upon first login"/>
-            <x14:filter val="Se debía acceder a la aplicación mientras se ejecutaba para verificar si tenía segregado los módulos de administración de los módulos de usuario, al revisar la aplicación no se encontraron módulos de administración"/>
-            <x14:filter val="se debía ejecutar la aplicación y navegar en ella para determinar si tiene canales de feedback dentro de sus vistas"/>
-            <x14:filter val="Se debía ingresar a la aplicación como un usuario del sistema y verificar que no se tenga acceso a funciones catalogadas como privilegiadas"/>
-            <x14:filter val="Se debía ingresar a la aplicación mobil luego de eliminar un usuario desde el backend para verificar que termine la sesion de usuario en curso"/>
-            <x14:filter val="Se debía ingresar al código fuente de la palicación para buscar si se usaba object deserialization using safe serialization APIs to prevent security vulnerabilities"/>
-            <x14:filter val="Se debía ingresar al código fuente de la palicación para buscar si se usaba object serialization using safe serialization APIs to prevent security vulnerabilities"/>
-            <x14:filter val="Se ingresó a la aplicación del servidor web y se comparó con la autenticación de la app móvil y son iguales, usuario y contraseña"/>
-            <x14:filter val="Se ingresó al backend de la aplicación y se verifica que the Web application uses as back-end, implements by default 7 failed attempts to block a user's account"/>
-            <x14:filter val="Se realizó una búsqueda en el código fuente y no implementations were found for calls to methods such as System.loadLibrary(), DexClassLoader, or any reflection technique that allows classes to be loaded dynamically from external locations"/>
-            <x14:filter val="Se requería verificar que la aplicación en tiempo de ejecución al ingresar tres veces consecutivas las credenciales incorrectas, realice el bloqueo respectivo"/>
-            <x14:filter val="Se requería verificar solo se validen las credenciales de manera conjunta al intentar autenticarse"/>
-            <x14:filter val="Se requirió cerrar sesión desde la aplicación para verificar que se muestre el mensaje de logout  existoso"/>
-            <x14:filter val="Se requirió correr la aplicación y verificar que la aplicación enmascara con asteriscos el password"/>
-            <x14:filter val="Se requirió revisar la funcionalidad de la aplicación en modo de ejecución para corroborar si incluye controles biométricos como FaceID and TouchID"/>
-            <x14:filter val="se requirió un escaneo del backend web de la aplicación para descartar vulnerabilidades asocioadas con poor randomization and incidents of loss of access to generated tokens in endpoints"/>
-            <x14:filter val="Se requirió un escaneo del backend web de la aplicación para descartar vulnerabilities associated with a lack of authentication and authorization prior to granting access to protected resources"/>
-            <x14:filter val="Se requirió una ejecución de la aplicación en tiempo real y se verifica que log out after a period of inactivity to prevent unauthorized access, particularly in high-risk locations or when handling sensitive data"/>
-            <x14:filter val="Se requirió una revisión de código para descartar el uso de device identifiers or geolocation data, for user authentication"/>
-            <x14:filter val="Se requirió una revisión del código de la aplicación donde se verificó the use of permission management functionality using the PermissionsDispatcher library and its constructPermissionsRequest method, which allows for runtime management of permissions for accessing the camera and external storage"/>
-            <x14:filter val="Se requirió una revisión del código de la aplicación para verificar que no se implemente Webviews ni JS por lo que output sanitization measures to prevent cross-site scripting (XSS) attacks no es aplicable, presenta seguridad por diseño"/>
-            <x14:filter val="Se requirió verificar los permisos por cada usuario y a que módulos podía acceder a fin de evaluar el control"/>
-            <x14:filter val="Se requirió verificar que application identifiers are not displayed until the log-on process has been successfully completed"/>
-            <x14:filter val="Se tuvo que ingresar al backend de la aplicación. y se verifica que the application, through the user and role management web module, implements a role-based access control (RBAC) mechanism for authorization, independent of authentication mechanisms. It also allows permissions to be assigned to modules based on the user"/>
-          </mc:Choice>
-          <mc:Fallback>
-            <filter val="Fue necesaria una inspección de código en la que se detectó que existía una posibilidad de command injection"/>
-            <filter val="Fue necesaria una revisión del código fuente de la aplicación y  the application code reveals no functionality to capture the user's most recent activity date"/>
-            <filter val="fue necesario acceder al código de la aplicación Android para verificar que has been verified that in the AndroidManifest.xml file a BroadcastReceiver has the configuration android:exported=&quot;false&quot;"/>
-            <filter val="Fue necesario acceder al código fuente de la aplicación y verificar que no se ocupen modos deprecados, for instance  MODE_WORLD_READABLE is not implemented, nor was the use of sockets identified, therefore the requirement is met"/>
-            <filter val="Fue necesario buscar en el código fuente de la aplicación para evidenciar que no se implementa llamadas a System.loadLibrary(), DexClassLoader, por lo tanto cumple con seguridad por diseño"/>
-            <filter val="Fue necesario desinstalar la aplicación de manera manual y verificar vía comandos que confidential user data are deleted luego de desinstalar"/>
-            <filter val="Fue necesario ejecutar la aplicación y evaluar si al pasar a segundo plano se limpiaba los datos sensibles, al ejecutar no superó la prueba"/>
-            <filter val="Fue necesario ingresar al Backend de la aplicación y verificar se implementen procedimientos de gestión de contraseñas seguras"/>
-            <filter val="Fue necesario ingresar al código de la aplicación Android y verificar que  BroadcastReceiver with the android:exported=&quot;false&quot; configuration has been detected in the AndroidManifest.xml file"/>
-            <filter val="Fue necesario ingresar al código fuente de la aplicación y dentro del fichero AndroidManifest.xml se evidenció que no user-defined permissions or new permissions outside of the standard ones are being used"/>
-            <filter val="Fue necesario ingresar al código fuente de la aplicación y en el build.gradle no se detectó llamadas a código nativo. Adicionalmente no se tiene hallazgos de manejo inseguro de memoria"/>
-            <filter val="Fue necesario ingresar al cóigo fuente de la aplicación y erificar que no se encuentra habilitado JS, por lo que cumpliría a través de diseño seguro por defecto"/>
-            <filter val="Fue necesario ingresar y revisar el código fuente para detectar si se implementa factor doble autenticación FMA, o SMS sendig, por lo que al no existir dicha funcionalidad, no existe vector de ataque"/>
-            <filter val="Fue necesario inspeccionar el código fuente para verificar si se encontraba en primera instancia habilitado o no webviews, al no encontrarse implementada esta funcionalidad, se declara cumplimiento puesto que no hay vector de ataque"/>
-            <filter val="Fue necesario realizar un análisis de código dinámico al backend de la aplicación web para verificar que hay missing headers and configurations in the backend to better manage http/https requests"/>
-            <filter val="Fue necesario revisar el código fuente de la aplicación y se encontró que no se tiene habilitado JS ni Webviews, debido a seguridad por diseño no se tienen vectores de ataque sobre carga dinámica de código"/>
-            <filter val="Fue necesario revisar el código fuente minuciosamente para verificar que  the session ID is not being used in the URL in HTTP requests"/>
-            <filter val="Fue necesario revisar la documentación el Backend de la aplicación para evidenciar que eisten controles para consumir las apis expuestas"/>
-            <filter val="Fue necesario revisar la documentación y código fuente y there is no evidence of explicit segregation in storage or configuration/control files in a directory separate from user data"/>
-            <filter val="Fue necesario revisar la funcionalidad de la aplicación web backend y there is a function to match patients by certain criteria, including UUID"/>
-            <filter val="Fue necesario un escaneo del backend de la aplicación para detectar si habría issues sobre manejo inadecuado de memoria como use-after-free errors , no se encontraron issues"/>
-            <filter val="Fue necesario un escaneo del backend de la aplicación para detectar si habría issues sobre manejo inadecuado de memoria, no se encontraron issues"/>
-            <filter val="Fue necesario una inspección del código fuente de la aplicación para detectar que la característica de no toucheable no se encontraba implementada, por lo que no prevendría prevent tapjacking attacks"/>
-            <filter val="Fue necesario una instalación de teclados de terceras personas y verificar que la aplicación no permita el ingreso de datos desde el mismo"/>
-            <filter val="Fue necesario verificar que la aplicación emplee mecanismos adicionales para asegurar las solicitudes de red basadas en protocolo http"/>
-            <filter val="Fue necesario verificar que la aplicación en tiempo de ejecución emplee credenciales únicas para autenticación, en este caso se usa usuario y password"/>
-            <filter val="Fuen necesario correr la aplicación para verificar que running the app, we observed that the clipboard allows users to copy and paste the username and password for login"/>
-            <filter val="No se encontraron vulnerabilidades asociadas a desbordamiento de buffer al realizar un escaneo del backend de la aplicación, así mismo no se encontró la vulnerabilidad en el código fuente de la apk"/>
-            <filter val="requería acceder al código fuente, buscar la implementación de SSLSocketFactory  y verificar que se cumpla con la medida de seguridad checkServerTrusted"/>
-            <filter val="Requería ingresar a la aplicación y verificar que durante la frase de autenticación no se muestren mensajes de ayuda ni feedbak"/>
-            <filter val="requirió a validation of the code signature via comandos para confirmar el cumplimiento"/>
-            <filter val="requirió navegar en el código fuente de la aplicación para verificar si key credentials are loaded securely using environment variables"/>
-            <filter val="Requirió revisar el código de la aplicación y no mechanisms have been found to restrict connection times to high-risk EHRi services to improve security and minimize the risk of unauthorized access"/>
-            <filter val="Requirió una revisión manual code, and it is verified that WebViews functionality is not implemented, therefore, control is considered to be fulfilled by design"/>
-            <filter val="Requirió una revisión y análisis de la funcionalidad, consecuentemente no se encontraron mecanismos para restrict connection times to high-risk EHRi services to enhance security and minimize the risk of unauthorized access"/>
-            <filter val="Se accedió al backend de la aplicación para gestión de usuarios y se pudo comprobar que se permite configure temporary passwords, which require an immediate change to a permanent password upon first login"/>
-            <filter val="Se debía acceder a la aplicación mientras se ejecutaba para verificar si tenía segregado los módulos de administración de los módulos de usuario, al revisar la aplicación no se encontraron módulos de administración"/>
-            <filter val="se debía ejecutar la aplicación y navegar en ella para determinar si tiene canales de feedback dentro de sus vistas"/>
-            <filter val="Se debía ingresar a la aplicación como un usuario del sistema y verificar que no se tenga acceso a funciones catalogadas como privilegiadas"/>
-            <filter val="Se debía ingresar a la aplicación mobil luego de eliminar un usuario desde el backend para verificar que termine la sesion de usuario en curso"/>
-            <filter val="Se debía ingresar al código fuente de la palicación para buscar si se usaba object deserialization using safe serialization APIs to prevent security vulnerabilities"/>
-            <filter val="Se debía ingresar al código fuente de la palicación para buscar si se usaba object serialization using safe serialization APIs to prevent security vulnerabilities"/>
-            <filter val="Se ingresó a la aplicación del servidor web y se comparó con la autenticación de la app móvil y son iguales, usuario y contraseña"/>
-            <filter val="Se ingresó al backend de la aplicación y se verifica que the Web application uses as back-end, implements by default 7 failed attempts to block a user's account"/>
-            <filter val="Se realizó una búsqueda en el código fuente y no implementations were found for calls to methods such as System.loadLibrary(), DexClassLoader, or any reflection technique that allows classes to be loaded dynamically from external locations"/>
-            <filter val="Se requería verificar que la aplicación en tiempo de ejecución al ingresar tres veces consecutivas las credenciales incorrectas, realice el bloqueo respectivo"/>
-            <filter val="Se requería verificar solo se validen las credenciales de manera conjunta al intentar autenticarse"/>
-            <filter val="Se requirió cerrar sesión desde la aplicación para verificar que se muestre el mensaje de logout  existoso"/>
-            <filter val="Se requirió correr la aplicación y verificar que la aplicación enmascara con asteriscos el password"/>
-            <filter val="Se requirió revisar la funcionalidad de la aplicación en modo de ejecución para corroborar si incluye controles biométricos como FaceID and TouchID"/>
-            <filter val="se requirió un escaneo del backend web de la aplicación para descartar vulnerabilidades asocioadas con poor randomization and incidents of loss of access to generated tokens in endpoints"/>
-            <filter val="Se requirió un escaneo del backend web de la aplicación para descartar vulnerabilities associated with a lack of authentication and authorization prior to granting access to protected resources"/>
-            <filter val="Se requirió una ejecución de la aplicación en tiempo real y se verifica que log out after a period of inactivity to prevent unauthorized access, particularly in high-risk locations or when handling sensitive data"/>
-            <filter val="Se requirió una revisión de código para descartar el uso de device identifiers or geolocation data, for user authentication"/>
-            <filter val="Se requirió una revisión del código de la aplicación para verificar que no se implemente Webviews ni JS por lo que output sanitization measures to prevent cross-site scripting (XSS) attacks no es aplicable, presenta seguridad por diseño"/>
-            <filter val="Se requirió verificar los permisos por cada usuario y a que módulos podía acceder a fin de evaluar el control"/>
-            <filter val="Se requirió verificar que application identifiers are not displayed until the log-on process has been successfully completed"/>
-          </mc:Fallback>
-        </mc:AlternateContent>
+        <filter val="yes"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2220,16 +2094,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E470"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2246,7 +2120,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2264,7 +2138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -2282,7 +2156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2300,7 +2174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -2318,7 +2192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2336,7 +2210,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -2354,7 +2228,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -2371,7 +2245,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2389,7 +2263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -2407,7 +2281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -2425,7 +2299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -2443,7 +2317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -2461,7 +2335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -2479,7 +2353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
@@ -2497,7 +2371,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -2515,7 +2389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -2533,7 +2407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -2551,7 +2425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -2568,7 +2442,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
@@ -2586,7 +2460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
@@ -2604,7 +2478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
@@ -2622,7 +2496,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
@@ -2640,7 +2514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
@@ -2658,7 +2532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
@@ -2675,7 +2549,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
@@ -2693,7 +2567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
@@ -2711,7 +2585,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
@@ -2729,7 +2603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
@@ -2747,7 +2621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -2765,7 +2639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
@@ -2783,7 +2657,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
@@ -2800,7 +2674,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
@@ -2818,7 +2692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
@@ -2836,7 +2710,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
@@ -2854,7 +2728,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
@@ -2872,7 +2746,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
@@ -2890,7 +2764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
@@ -2908,7 +2782,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>41</v>
       </c>
@@ -2926,7 +2800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>42</v>
       </c>
@@ -2944,7 +2818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
@@ -2962,7 +2836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>44</v>
       </c>
@@ -2980,7 +2854,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>45</v>
       </c>
@@ -2997,7 +2871,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>46</v>
       </c>
@@ -3015,7 +2889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>47</v>
       </c>
@@ -3033,7 +2907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>48</v>
       </c>
@@ -3051,7 +2925,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>49</v>
       </c>
@@ -3069,7 +2943,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>50</v>
       </c>
@@ -3087,7 +2961,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>51</v>
       </c>
@@ -3105,7 +2979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
@@ -3123,7 +2997,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>53</v>
       </c>
@@ -3141,7 +3015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>54</v>
       </c>
@@ -3159,7 +3033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>55</v>
       </c>
@@ -3177,7 +3051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>56</v>
       </c>
@@ -3195,7 +3069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>57</v>
       </c>
@@ -3213,7 +3087,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>58</v>
       </c>
@@ -3231,7 +3105,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>59</v>
       </c>
@@ -3249,7 +3123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>60</v>
       </c>
@@ -3266,7 +3140,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
@@ -3283,7 +3157,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>62</v>
       </c>
@@ -3301,7 +3175,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>63</v>
       </c>
@@ -3319,7 +3193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>64</v>
       </c>
@@ -3337,7 +3211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>65</v>
       </c>
@@ -3355,7 +3229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>66</v>
       </c>
@@ -3373,7 +3247,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>67</v>
       </c>
@@ -3391,7 +3265,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
@@ -3409,7 +3283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>69</v>
       </c>
@@ -3426,7 +3300,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>70</v>
       </c>
@@ -3443,7 +3317,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>71</v>
       </c>
@@ -3461,7 +3335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>72</v>
       </c>
@@ -3479,7 +3353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>73</v>
       </c>
@@ -3496,7 +3370,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>74</v>
       </c>
@@ -3513,7 +3387,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>75</v>
       </c>
@@ -3531,7 +3405,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>76</v>
       </c>
@@ -3548,7 +3422,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>77</v>
       </c>
@@ -3565,7 +3439,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
@@ -3583,7 +3457,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>79</v>
       </c>
@@ -3601,7 +3475,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>80</v>
       </c>
@@ -3619,7 +3493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>81</v>
       </c>
@@ -3637,7 +3511,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>82</v>
       </c>
@@ -3655,7 +3529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>83</v>
       </c>
@@ -3673,7 +3547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>84</v>
       </c>
@@ -3691,7 +3565,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>85</v>
       </c>
@@ -3709,7 +3583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>86</v>
       </c>
@@ -3727,7 +3601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>87</v>
       </c>
@@ -3745,7 +3619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>88</v>
       </c>
@@ -3763,7 +3637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>89</v>
       </c>
@@ -3781,7 +3655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>90</v>
       </c>
@@ -3798,7 +3672,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>91</v>
       </c>
@@ -3816,7 +3690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>92</v>
       </c>
@@ -3833,7 +3707,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>93</v>
       </c>
@@ -3850,7 +3724,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>94</v>
       </c>
@@ -3868,7 +3742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>95</v>
       </c>
@@ -3886,7 +3760,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>96</v>
       </c>
@@ -3904,7 +3778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>97</v>
       </c>
@@ -3922,7 +3796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>98</v>
       </c>
@@ -3940,7 +3814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>99</v>
       </c>
@@ -3958,7 +3832,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>100</v>
       </c>
@@ -3976,7 +3850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>101</v>
       </c>
@@ -3994,7 +3868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>102</v>
       </c>
@@ -4011,7 +3885,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>103</v>
       </c>
@@ -4029,7 +3903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>104</v>
       </c>
@@ -4047,7 +3921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>105</v>
       </c>
@@ -4065,7 +3939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>106</v>
       </c>
@@ -4083,7 +3957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>107</v>
       </c>
@@ -4101,7 +3975,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>108</v>
       </c>
@@ -4119,7 +3993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>109</v>
       </c>
@@ -4137,7 +4011,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>110</v>
       </c>
@@ -4155,7 +4029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>111</v>
       </c>
@@ -4173,7 +4047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>112</v>
       </c>
@@ -4190,7 +4064,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>113</v>
       </c>
@@ -4208,7 +4082,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>114</v>
       </c>
@@ -4226,7 +4100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>115</v>
       </c>
@@ -4244,7 +4118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>116</v>
       </c>
@@ -4262,7 +4136,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>117</v>
       </c>
@@ -4280,7 +4154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>118</v>
       </c>
@@ -4297,7 +4171,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>119</v>
       </c>
@@ -4314,7 +4188,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>120</v>
       </c>
@@ -4332,7 +4206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>121</v>
       </c>
@@ -4350,7 +4224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>122</v>
       </c>
@@ -4368,7 +4242,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>123</v>
       </c>
@@ -4386,7 +4260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>124</v>
       </c>
@@ -4404,7 +4278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>125</v>
       </c>
@@ -4422,7 +4296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>126</v>
       </c>
@@ -4440,7 +4314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>127</v>
       </c>
@@ -4458,7 +4332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>128</v>
       </c>
@@ -4476,7 +4350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>129</v>
       </c>
@@ -4494,7 +4368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>130</v>
       </c>
@@ -4512,7 +4386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>131</v>
       </c>
@@ -4530,7 +4404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>132</v>
       </c>
@@ -4548,7 +4422,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>133</v>
       </c>
@@ -4566,7 +4440,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>134</v>
       </c>
@@ -4584,7 +4458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>135</v>
       </c>
@@ -4602,7 +4476,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>136</v>
       </c>
@@ -4620,7 +4494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>137</v>
       </c>
@@ -4638,7 +4512,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>138</v>
       </c>
@@ -4656,7 +4530,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>139</v>
       </c>
@@ -4674,7 +4548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>140</v>
       </c>
@@ -4692,7 +4566,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>141</v>
       </c>
@@ -4709,7 +4583,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>142</v>
       </c>
@@ -4726,7 +4600,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>143</v>
       </c>
@@ -4744,7 +4618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>144</v>
       </c>
@@ -4762,7 +4636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>145</v>
       </c>
@@ -4780,7 +4654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>146</v>
       </c>
@@ -4797,7 +4671,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>147</v>
       </c>
@@ -4815,7 +4689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>148</v>
       </c>
@@ -4833,7 +4707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>149</v>
       </c>
@@ -4851,7 +4725,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>150</v>
       </c>
@@ -4869,7 +4743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>151</v>
       </c>
@@ -4887,7 +4761,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>152</v>
       </c>
@@ -4905,7 +4779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>153</v>
       </c>
@@ -4923,7 +4797,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>154</v>
       </c>
@@ -4941,7 +4815,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>155</v>
       </c>
@@ -4959,7 +4833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>156</v>
       </c>
@@ -4977,7 +4851,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>157</v>
       </c>
@@ -4995,7 +4869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>158</v>
       </c>
@@ -5013,7 +4887,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>159</v>
       </c>
@@ -5030,7 +4904,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>160</v>
       </c>
@@ -5047,7 +4921,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>161</v>
       </c>
@@ -5065,7 +4939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>162</v>
       </c>
@@ -5082,7 +4956,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>163</v>
       </c>
@@ -5100,7 +4974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>164</v>
       </c>
@@ -5118,7 +4992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>165</v>
       </c>
@@ -5136,7 +5010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>166</v>
       </c>
@@ -5153,7 +5027,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>167</v>
       </c>
@@ -5171,7 +5045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>168</v>
       </c>
@@ -5189,7 +5063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>169</v>
       </c>
@@ -5207,7 +5081,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>170</v>
       </c>
@@ -5225,7 +5099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>171</v>
       </c>
@@ -5243,7 +5117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>172</v>
       </c>
@@ -5261,7 +5135,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>173</v>
       </c>
@@ -5279,7 +5153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>174</v>
       </c>
@@ -5297,7 +5171,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>175</v>
       </c>
@@ -5315,7 +5189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>176</v>
       </c>
@@ -5332,7 +5206,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>177</v>
       </c>
@@ -5350,7 +5224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>178</v>
       </c>
@@ -5368,7 +5242,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>179</v>
       </c>
@@ -5386,7 +5260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>180</v>
       </c>
@@ -5394,16 +5268,17 @@
         <v>8</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E178" s="12" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="D178" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>no</v>
+      </c>
+      <c r="E178" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>181</v>
       </c>
@@ -5417,10 +5292,10 @@
         <v>8</v>
       </c>
       <c r="E179" s="12" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>182</v>
       </c>
@@ -5438,7 +5313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>183</v>
       </c>
@@ -5452,10 +5327,10 @@
         <v>8</v>
       </c>
       <c r="E181" s="12" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>184</v>
       </c>
@@ -5473,7 +5348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>185</v>
       </c>
@@ -5491,7 +5366,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>186</v>
       </c>
@@ -5509,7 +5384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>187</v>
       </c>
@@ -5527,7 +5402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>188</v>
       </c>
@@ -5545,7 +5420,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>189</v>
       </c>
@@ -5563,7 +5438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>190</v>
       </c>
@@ -5581,7 +5456,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>191</v>
       </c>
@@ -5599,7 +5474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>192</v>
       </c>
@@ -5617,7 +5492,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>193</v>
       </c>
@@ -5635,7 +5510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>194</v>
       </c>
@@ -5649,10 +5524,10 @@
         <v>8</v>
       </c>
       <c r="E192" s="12" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>195</v>
       </c>
@@ -5670,7 +5545,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>196</v>
       </c>
@@ -5688,7 +5563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>197</v>
       </c>
@@ -5706,7 +5581,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>198</v>
       </c>
@@ -5724,7 +5599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>199</v>
       </c>
@@ -5742,7 +5617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>200</v>
       </c>
@@ -5760,7 +5635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>201</v>
       </c>
@@ -5774,10 +5649,10 @@
         <v>8</v>
       </c>
       <c r="E199" s="12" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>202</v>
       </c>
@@ -5795,7 +5670,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>203</v>
       </c>
@@ -5813,7 +5688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>204</v>
       </c>
@@ -5831,7 +5706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>205</v>
       </c>
@@ -5849,7 +5724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>206</v>
       </c>
@@ -5867,7 +5742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>207</v>
       </c>
@@ -5885,7 +5760,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>208</v>
       </c>
@@ -5903,7 +5778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>209</v>
       </c>
@@ -5921,7 +5796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>210</v>
       </c>
@@ -5939,7 +5814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>211</v>
       </c>
@@ -5957,7 +5832,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>212</v>
       </c>
@@ -5975,7 +5850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>213</v>
       </c>
@@ -5989,10 +5864,10 @@
         <v>8</v>
       </c>
       <c r="E211" s="12" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>214</v>
       </c>
@@ -6006,10 +5881,10 @@
         <v>8</v>
       </c>
       <c r="E212" s="12" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>215</v>
       </c>
@@ -6023,10 +5898,10 @@
         <v>8</v>
       </c>
       <c r="E213" s="12" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>216</v>
       </c>
@@ -6044,7 +5919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>217</v>
       </c>
@@ -6062,7 +5937,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>218</v>
       </c>
@@ -6080,7 +5955,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>219</v>
       </c>
@@ -6098,7 +5973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>220</v>
       </c>
@@ -6116,7 +5991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>221</v>
       </c>
@@ -6130,10 +6005,10 @@
         <v>8</v>
       </c>
       <c r="E219" s="12" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>222</v>
       </c>
@@ -6151,7 +6026,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="135" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>223</v>
       </c>
@@ -6165,10 +6040,10 @@
         <v>8</v>
       </c>
       <c r="E221" s="12" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>224</v>
       </c>
@@ -6186,7 +6061,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>225</v>
       </c>
@@ -6204,7 +6079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>226</v>
       </c>
@@ -6222,7 +6097,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>227</v>
       </c>
@@ -6240,7 +6115,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>228</v>
       </c>
@@ -6258,7 +6133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>229</v>
       </c>
@@ -6276,7 +6151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>230</v>
       </c>
@@ -6294,7 +6169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>231</v>
       </c>
@@ -6312,7 +6187,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>232</v>
       </c>
@@ -6330,7 +6205,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>233</v>
       </c>
@@ -6348,7 +6223,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>234</v>
       </c>
@@ -6366,7 +6241,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>235</v>
       </c>
@@ -6380,10 +6255,10 @@
         <v>8</v>
       </c>
       <c r="E233" s="12" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>236</v>
       </c>
@@ -6397,10 +6272,10 @@
         <v>8</v>
       </c>
       <c r="E234" s="12" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>237</v>
       </c>
@@ -6418,7 +6293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>238</v>
       </c>
@@ -6436,7 +6311,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>239</v>
       </c>
@@ -6454,7 +6329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>240</v>
       </c>
@@ -6472,7 +6347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>241</v>
       </c>
@@ -6490,7 +6365,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>242</v>
       </c>
@@ -6508,7 +6383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>243</v>
       </c>
@@ -6526,7 +6401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>244</v>
       </c>
@@ -6544,7 +6419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>245</v>
       </c>
@@ -6562,7 +6437,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>246</v>
       </c>
@@ -6580,7 +6455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>247</v>
       </c>
@@ -6594,10 +6469,10 @@
         <v>8</v>
       </c>
       <c r="E245" s="12" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>248</v>
       </c>
@@ -6615,7 +6490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>249</v>
       </c>
@@ -6633,7 +6508,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>250</v>
       </c>
@@ -6647,10 +6522,10 @@
         <v>8</v>
       </c>
       <c r="E248" s="12" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>251</v>
       </c>
@@ -6668,7 +6543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>252</v>
       </c>
@@ -6686,7 +6561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>253</v>
       </c>
@@ -6704,7 +6579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>254</v>
       </c>
@@ -6722,7 +6597,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>255</v>
       </c>
@@ -6740,7 +6615,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>256</v>
       </c>
@@ -6758,7 +6633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>257</v>
       </c>
@@ -6776,7 +6651,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>258</v>
       </c>
@@ -6794,7 +6669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>259</v>
       </c>
@@ -6812,7 +6687,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>260</v>
       </c>
@@ -6830,7 +6705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>261</v>
       </c>
@@ -6848,7 +6723,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>262</v>
       </c>
@@ -6866,7 +6741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>263</v>
       </c>
@@ -6880,10 +6755,10 @@
         <v>8</v>
       </c>
       <c r="E261" s="12" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>264</v>
       </c>
@@ -6901,7 +6776,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>265</v>
       </c>
@@ -6919,7 +6794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>266</v>
       </c>
@@ -6937,7 +6812,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>267</v>
       </c>
@@ -6955,7 +6830,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>268</v>
       </c>
@@ -6973,7 +6848,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>269</v>
       </c>
@@ -6991,7 +6866,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>270</v>
       </c>
@@ -7009,7 +6884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>271</v>
       </c>
@@ -7027,7 +6902,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>272</v>
       </c>
@@ -7045,7 +6920,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>273</v>
       </c>
@@ -7063,7 +6938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>274</v>
       </c>
@@ -7081,7 +6956,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>275</v>
       </c>
@@ -7099,7 +6974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>276</v>
       </c>
@@ -7117,7 +6992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>277</v>
       </c>
@@ -7135,7 +7010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>278</v>
       </c>
@@ -7153,7 +7028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>279</v>
       </c>
@@ -7171,7 +7046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>280</v>
       </c>
@@ -7189,7 +7064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>281</v>
       </c>
@@ -7207,7 +7082,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>282</v>
       </c>
@@ -7225,7 +7100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>283</v>
       </c>
@@ -7239,10 +7114,10 @@
         <v>8</v>
       </c>
       <c r="E281" s="12" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>284</v>
       </c>
@@ -7256,10 +7131,10 @@
         <v>8</v>
       </c>
       <c r="E282" s="12" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>285</v>
       </c>
@@ -7277,7 +7152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>286</v>
       </c>
@@ -7295,7 +7170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>287</v>
       </c>
@@ -7313,7 +7188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>288</v>
       </c>
@@ -7331,7 +7206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>289</v>
       </c>
@@ -7349,7 +7224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>290</v>
       </c>
@@ -7367,7 +7242,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>291</v>
       </c>
@@ -7385,7 +7260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>292</v>
       </c>
@@ -7403,7 +7278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>293</v>
       </c>
@@ -7421,7 +7296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>294</v>
       </c>
@@ -7439,7 +7314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>295</v>
       </c>
@@ -7457,7 +7332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>296</v>
       </c>
@@ -7475,7 +7350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>297</v>
       </c>
@@ -7493,7 +7368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>298</v>
       </c>
@@ -7511,7 +7386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>299</v>
       </c>
@@ -7529,7 +7404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>300</v>
       </c>
@@ -7547,7 +7422,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>301</v>
       </c>
@@ -7561,10 +7436,10 @@
         <v>8</v>
       </c>
       <c r="E299" s="12" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>302</v>
       </c>
@@ -7582,7 +7457,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>303</v>
       </c>
@@ -7600,7 +7475,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>304</v>
       </c>
@@ -7618,7 +7493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>305</v>
       </c>
@@ -7632,10 +7507,10 @@
         <v>8</v>
       </c>
       <c r="E303" s="12" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>306</v>
       </c>
@@ -7649,10 +7524,10 @@
         <v>8</v>
       </c>
       <c r="E304" s="12" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>307</v>
       </c>
@@ -7666,10 +7541,10 @@
         <v>8</v>
       </c>
       <c r="E305" s="12" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>308</v>
       </c>
@@ -7683,10 +7558,10 @@
         <v>8</v>
       </c>
       <c r="E306" s="12" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>309</v>
       </c>
@@ -7700,10 +7575,10 @@
         <v>8</v>
       </c>
       <c r="E307" s="12" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>310</v>
       </c>
@@ -7717,10 +7592,10 @@
         <v>8</v>
       </c>
       <c r="E308" s="12" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>311</v>
       </c>
@@ -7734,10 +7609,10 @@
         <v>8</v>
       </c>
       <c r="E309" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>312</v>
       </c>
@@ -7751,10 +7626,10 @@
         <v>8</v>
       </c>
       <c r="E310" s="12" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>313</v>
       </c>
@@ -7768,10 +7643,10 @@
         <v>8</v>
       </c>
       <c r="E311" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>314</v>
       </c>
@@ -7789,7 +7664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>315</v>
       </c>
@@ -7807,7 +7682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>316</v>
       </c>
@@ -7821,10 +7696,10 @@
         <v>8</v>
       </c>
       <c r="E314" s="12" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>317</v>
       </c>
@@ -7838,10 +7713,10 @@
         <v>8</v>
       </c>
       <c r="E315" s="12" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>318</v>
       </c>
@@ -7859,7 +7734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>319</v>
       </c>
@@ -7877,7 +7752,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>320</v>
       </c>
@@ -7891,10 +7766,10 @@
         <v>8</v>
       </c>
       <c r="E318" s="12" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>321</v>
       </c>
@@ -7912,7 +7787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>322</v>
       </c>
@@ -7930,7 +7805,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>323</v>
       </c>
@@ -7948,7 +7823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>324</v>
       </c>
@@ -7966,7 +7841,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>325</v>
       </c>
@@ -7984,7 +7859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>326</v>
       </c>
@@ -8002,7 +7877,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>327</v>
       </c>
@@ -8020,7 +7895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>328</v>
       </c>
@@ -8038,7 +7913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>329</v>
       </c>
@@ -8056,7 +7931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>330</v>
       </c>
@@ -8074,7 +7949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>331</v>
       </c>
@@ -8092,7 +7967,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>332</v>
       </c>
@@ -8110,7 +7985,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>333</v>
       </c>
@@ -8128,7 +8003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>334</v>
       </c>
@@ -8146,7 +8021,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>335</v>
       </c>
@@ -8164,7 +8039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>336</v>
       </c>
@@ -8178,10 +8053,10 @@
         <v>8</v>
       </c>
       <c r="E334" s="12" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>337</v>
       </c>
@@ -8199,7 +8074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>338</v>
       </c>
@@ -8217,7 +8092,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>339</v>
       </c>
@@ -8235,7 +8110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>340</v>
       </c>
@@ -8253,7 +8128,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>341</v>
       </c>
@@ -8267,10 +8142,10 @@
         <v>8</v>
       </c>
       <c r="E339" s="12" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>342</v>
       </c>
@@ -8288,7 +8163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>343</v>
       </c>
@@ -8306,7 +8181,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>344</v>
       </c>
@@ -8324,7 +8199,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>345</v>
       </c>
@@ -8342,7 +8217,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>346</v>
       </c>
@@ -8360,7 +8235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>347</v>
       </c>
@@ -8378,7 +8253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>348</v>
       </c>
@@ -8396,7 +8271,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>349</v>
       </c>
@@ -8414,7 +8289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>350</v>
       </c>
@@ -8432,7 +8307,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>351</v>
       </c>
@@ -8450,7 +8325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>352</v>
       </c>
@@ -8468,7 +8343,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>353</v>
       </c>
@@ -8486,7 +8361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>354</v>
       </c>
@@ -8504,7 +8379,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>355</v>
       </c>
@@ -8522,7 +8397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>356</v>
       </c>
@@ -8536,10 +8411,10 @@
         <v>8</v>
       </c>
       <c r="E354" s="12" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>357</v>
       </c>
@@ -8557,7 +8432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>358</v>
       </c>
@@ -8575,7 +8450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>359</v>
       </c>
@@ -8593,7 +8468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>360</v>
       </c>
@@ -8611,7 +8486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>361</v>
       </c>
@@ -8629,7 +8504,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>362</v>
       </c>
@@ -8647,7 +8522,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>363</v>
       </c>
@@ -8665,7 +8540,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>364</v>
       </c>
@@ -8683,7 +8558,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>365</v>
       </c>
@@ -8701,7 +8576,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>366</v>
       </c>
@@ -8719,7 +8594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>367</v>
       </c>
@@ -8737,7 +8612,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>368</v>
       </c>
@@ -8755,7 +8630,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>369</v>
       </c>
@@ -8773,7 +8648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>370</v>
       </c>
@@ -8791,7 +8666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>371</v>
       </c>
@@ -8809,7 +8684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>372</v>
       </c>
@@ -8827,7 +8702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>373</v>
       </c>
@@ -8845,7 +8720,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>374</v>
       </c>
@@ -8863,7 +8738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>375</v>
       </c>
@@ -8881,7 +8756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>376</v>
       </c>
@@ -8899,7 +8774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>377</v>
       </c>
@@ -8917,7 +8792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>378</v>
       </c>
@@ -8935,7 +8810,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>379</v>
       </c>
@@ -8953,7 +8828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>380</v>
       </c>
@@ -8971,7 +8846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>381</v>
       </c>
@@ -8989,7 +8864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>382</v>
       </c>
@@ -9007,7 +8882,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>383</v>
       </c>
@@ -9025,7 +8900,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>384</v>
       </c>
@@ -9043,7 +8918,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>385</v>
       </c>
@@ -9061,7 +8936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>386</v>
       </c>
@@ -9079,7 +8954,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>387</v>
       </c>
@@ -9097,7 +8972,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>388</v>
       </c>
@@ -9115,7 +8990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>389</v>
       </c>
@@ -9133,7 +9008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>390</v>
       </c>
@@ -9151,7 +9026,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>391</v>
       </c>
@@ -9169,7 +9044,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>392</v>
       </c>
@@ -9187,7 +9062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>393</v>
       </c>
@@ -9205,7 +9080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>394</v>
       </c>
@@ -9223,7 +9098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>395</v>
       </c>
@@ -9241,7 +9116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>396</v>
       </c>
@@ -9259,7 +9134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>397</v>
       </c>
@@ -9277,7 +9152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>398</v>
       </c>
@@ -9295,7 +9170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>399</v>
       </c>
@@ -9313,7 +9188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>400</v>
       </c>
@@ -9331,7 +9206,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>401</v>
       </c>
@@ -9349,7 +9224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>402</v>
       </c>
@@ -9367,7 +9242,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>403</v>
       </c>
@@ -9385,7 +9260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>404</v>
       </c>
@@ -9403,7 +9278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>405</v>
       </c>
@@ -9421,7 +9296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>406</v>
       </c>
@@ -9439,7 +9314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>407</v>
       </c>
@@ -9457,7 +9332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>408</v>
       </c>
@@ -9475,7 +9350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>409</v>
       </c>
@@ -9493,7 +9368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>410</v>
       </c>
@@ -9511,7 +9386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>411</v>
       </c>
@@ -9529,7 +9404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>412</v>
       </c>
@@ -9547,7 +9422,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>413</v>
       </c>
@@ -9561,10 +9436,10 @@
         <v>8</v>
       </c>
       <c r="E411" s="12" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="412" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>414</v>
       </c>
@@ -9578,10 +9453,10 @@
         <v>8</v>
       </c>
       <c r="E412" s="12" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>415</v>
       </c>
@@ -9599,7 +9474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>416</v>
       </c>
@@ -9617,7 +9492,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>417</v>
       </c>
@@ -9635,7 +9510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>418</v>
       </c>
@@ -9653,7 +9528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>419</v>
       </c>
@@ -9671,7 +9546,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>420</v>
       </c>
@@ -9689,7 +9564,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>421</v>
       </c>
@@ -9707,7 +9582,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>422</v>
       </c>
@@ -9715,17 +9590,16 @@
         <v>8</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D420" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>no</v>
-      </c>
-      <c r="E420" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="D420" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E420" s="12" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>423</v>
       </c>
@@ -9743,7 +9617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>424</v>
       </c>
@@ -9761,7 +9635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>425</v>
       </c>
@@ -9779,7 +9653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>426</v>
       </c>
@@ -9793,10 +9667,10 @@
         <v>8</v>
       </c>
       <c r="E424" s="12" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>427</v>
       </c>
@@ -9814,7 +9688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>428</v>
       </c>
@@ -9832,7 +9706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>429</v>
       </c>
@@ -9850,7 +9724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>430</v>
       </c>
@@ -9868,7 +9742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>431</v>
       </c>
@@ -9886,7 +9760,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>432</v>
       </c>
@@ -9904,7 +9778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>433</v>
       </c>
@@ -9922,7 +9796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>434</v>
       </c>
@@ -9940,7 +9814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>435</v>
       </c>
@@ -9958,7 +9832,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>436</v>
       </c>
@@ -9976,7 +9850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>437</v>
       </c>
@@ -9994,7 +9868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>438</v>
       </c>
@@ -10012,7 +9886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>439</v>
       </c>
@@ -10030,7 +9904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>440</v>
       </c>
@@ -10048,7 +9922,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>441</v>
       </c>
@@ -10066,7 +9940,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>442</v>
       </c>
@@ -10084,7 +9958,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>443</v>
       </c>
@@ -10102,7 +9976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>444</v>
       </c>
@@ -10120,7 +9994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>445</v>
       </c>
@@ -10138,7 +10012,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>446</v>
       </c>
@@ -10156,7 +10030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>447</v>
       </c>
@@ -10174,7 +10048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>448</v>
       </c>
@@ -10188,10 +10062,10 @@
         <v>8</v>
       </c>
       <c r="E446" s="12" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>449</v>
       </c>
@@ -10209,7 +10083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>450</v>
       </c>
@@ -10227,7 +10101,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>451</v>
       </c>
@@ -10245,7 +10119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>452</v>
       </c>
@@ -10263,7 +10137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>453</v>
       </c>
@@ -10281,7 +10155,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>454</v>
       </c>
@@ -10299,7 +10173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>455</v>
       </c>
@@ -10317,7 +10191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>456</v>
       </c>
@@ -10335,7 +10209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>457</v>
       </c>
@@ -10353,7 +10227,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>458</v>
       </c>
@@ -10371,7 +10245,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>459</v>
       </c>
@@ -10389,7 +10263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>460</v>
       </c>
@@ -10407,7 +10281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>461</v>
       </c>
@@ -10425,7 +10299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>462</v>
       </c>
@@ -10443,7 +10317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>463</v>
       </c>
@@ -10461,7 +10335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>464</v>
       </c>
@@ -10475,10 +10349,10 @@
         <v>8</v>
       </c>
       <c r="E462" s="12" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>465</v>
       </c>
@@ -10496,7 +10370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>466</v>
       </c>
@@ -10514,7 +10388,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>467</v>
       </c>
@@ -10532,7 +10406,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>468</v>
       </c>
@@ -10550,7 +10424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>469</v>
       </c>
@@ -10568,7 +10442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>470</v>
       </c>
@@ -10586,7 +10460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>471</v>
       </c>
@@ -10604,7 +10478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>472</v>
       </c>
@@ -10633,15 +10507,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97C92A0-166F-48E2-B1C3-2920A4A2131B}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10658,7 +10532,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="90.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>60</v>
       </c>
@@ -10672,10 +10546,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>61</v>
       </c>
@@ -10689,10 +10563,10 @@
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>92</v>
       </c>
@@ -10709,7 +10583,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>93</v>
       </c>
@@ -10726,7 +10600,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>159</v>
       </c>
@@ -10743,7 +10617,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>160</v>
       </c>
@@ -10757,10 +10631,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>213</v>
       </c>
@@ -10774,10 +10648,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>214</v>
       </c>
@@ -10791,10 +10665,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>263</v>
       </c>
@@ -10808,10 +10682,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>284</v>
       </c>
@@ -10825,10 +10699,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>301</v>
       </c>
@@ -10842,10 +10716,10 @@
         <v>8</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>305</v>
       </c>
@@ -10859,10 +10733,10 @@
         <v>8</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>414</v>
       </c>
@@ -10876,10 +10750,10 @@
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>464</v>
       </c>
@@ -10893,7 +10767,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -10905,9 +10779,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0D3356-FC38-495F-B2A8-54C327FA87F6}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10924,7 +10798,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="101.4" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="120.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -10938,10 +10812,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="390" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -10955,10 +10829,10 @@
         <v>8</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
@@ -10972,10 +10846,10 @@
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>69</v>
       </c>
@@ -10989,10 +10863,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>70</v>
       </c>
@@ -11006,10 +10880,10 @@
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="225" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>74</v>
       </c>
@@ -11023,10 +10897,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>76</v>
       </c>
@@ -11040,10 +10914,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="255" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>77</v>
       </c>
@@ -11057,10 +10931,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>90</v>
       </c>
@@ -11074,10 +10948,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="225" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>112</v>
       </c>
@@ -11094,7 +10968,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>118</v>
       </c>
@@ -11111,7 +10985,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="360" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>119</v>
       </c>
@@ -11128,7 +11002,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="330" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>141</v>
       </c>
@@ -11145,7 +11019,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="285" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>142</v>
       </c>
@@ -11162,7 +11036,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>146</v>
       </c>
@@ -11179,7 +11053,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="315" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>166</v>
       </c>
@@ -11196,7 +11070,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="285" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>176</v>
       </c>
@@ -11213,60 +11087,60 @@
         <v>504</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="7" t="s">
+    <row r="19" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="10" t="s">
+    <row r="20" spans="1:5" ht="300" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="7" t="s">
+    <row r="21" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="150" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>8</v>
@@ -11278,46 +11152,46 @@
         <v>8</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="10" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="330" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="255" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>8</v>
@@ -11329,12 +11203,12 @@
         <v>8</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="240" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>8</v>
@@ -11346,63 +11220,63 @@
         <v>8</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="10" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+    <row r="28" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="B28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="270" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>8</v>
@@ -11417,60 +11291,60 @@
         <v>525</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="216" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="216" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+    <row r="31" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="B31" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="315" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="B32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="390" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="330" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>8</v>
@@ -11482,12 +11356,12 @@
         <v>8</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>8</v>
@@ -11499,12 +11373,12 @@
         <v>8</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="255" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>341</v>
+        <v>413</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>8</v>
@@ -11516,12 +11390,12 @@
         <v>8</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="330" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>8</v>
@@ -11533,10 +11407,10 @@
         <v>8</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="255" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>426</v>
       </c>
@@ -11550,10 +11424,10 @@
         <v>8</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="390" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>448</v>
       </c>
@@ -11567,7 +11441,7 @@
         <v>8</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -11579,9 +11453,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C002820-0DFF-4E49-B6F7-1BEF798CF8A7}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11598,7 +11472,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="245.4" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="270.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>20</v>
       </c>
@@ -11612,10 +11486,10 @@
         <v>473</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>27</v>
       </c>
@@ -11629,10 +11503,10 @@
         <v>473</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>73</v>
       </c>
@@ -11649,7 +11523,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>102</v>
       </c>
@@ -11666,7 +11540,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="240" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>162</v>
       </c>
@@ -11683,7 +11557,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="360" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>235</v>
       </c>
@@ -11697,10 +11571,10 @@
         <v>473</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>236</v>
       </c>
@@ -11714,10 +11588,10 @@
         <v>473</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>247</v>
       </c>
@@ -11731,10 +11605,10 @@
         <v>473</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="240" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>283</v>
       </c>
@@ -11748,10 +11622,10 @@
         <v>473</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="270" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>310</v>
       </c>
@@ -11765,10 +11639,10 @@
         <v>473</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="330" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>317</v>
       </c>
@@ -11782,10 +11656,10 @@
         <v>473</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="330" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>336</v>
       </c>
@@ -11799,10 +11673,10 @@
         <v>473</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="201.6" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="240" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>356</v>
       </c>
@@ -11816,7 +11690,7 @@
         <v>473</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -11828,9 +11702,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944C6E6A-D3DF-4D44-8CE4-A2F91A523130}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11847,7 +11721,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="331.8" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="375.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>201</v>
       </c>
@@ -11861,7 +11735,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
